--- a/results/job_matches_2026-09-24.xlsx
+++ b/results/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>eHealth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9741dbb2ec8505fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2f6705aae6b6275d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SPEC ADV SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0cab26aeb02c83</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54cc75b0d6eba6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435e38702075f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9741dbb2ec8505fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (.NET / Java Spring Boot / AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Oracle, SQL Server</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36f17458475becb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b60177884abfc7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0cab26aeb02c83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e85b1b7c04ae1c1</t>
+          <t>https://www.indeed.com/viewjob?jk=435e38702075f0bd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Architect (Dynamics 365 Copilot) (ONSITE in Vienna, VA)</t>
+          <t>Software Engineer 2 (.NET / Java Spring Boot / AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781e2cfbc6955c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f36f17458475becb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/Data Science Eng I</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
+          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
+          <t>https://www.indeed.com/viewjob?jk=7e85b1b7c04ae1c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6acf2339423ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
+          <t>https://www.indeed.com/viewjob?jk=ad026bf190602503</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6acf2339423ef7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 5 - Enterprise Risk Management</t>
+          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,38 +937,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
+          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Nexus Products</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
+          <t>https://www.indeed.com/viewjob?jk=e200e28931966534</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Payment Networks</t>
+          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,247 +1016,247 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - HR Tech</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
+          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
+          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer I, II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
+          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>iVedha Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Toronto, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
+          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Techsur Solutions</t>
+          <t>Giant Eagle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfb157f527b54b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
+          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
+          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer I, II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Cinemark</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
+          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iVedha Inc.</t>
+          <t>FMNE Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Toronto, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
+          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Associate Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Delta Dental</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
+          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Data Engineer (Oracle Apps)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
+          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cinemark</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FMNE Insurance Company</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
+          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Generative AI Technology</t>
+          <t>Backend Engineer: Retail Media</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
+          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=464f070dcc86c2c0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (Oracle Apps)</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
+          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Senior Platform Engineer, Growth Product Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Growth Product Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/AWS)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, PySpark, Scala, Spark Streaming, Kafka, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9afa06dd2d2419</t>
+          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AWS)</t>
+          <t>Sr. Data Integration Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>SPS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65da8aaf4011e226</t>
+          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AWS)</t>
+          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada06b5a2ee25a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AWS)</t>
+          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419115b4b37379d9</t>
+          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Station Casinos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=131c1627cfe23b10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
+          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Software Engineering Co-op (Cloud)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea49302adcd1e9c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
+          <t>Sr. Software Engineer - CloudOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Integration Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPS Health</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
+          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Palantir IT Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Station Casinos</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c1627cfe23b10</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full stack Developer-Boston, MA</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a357bae88f6db7</t>
+          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Workspaces Migration Architect</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1680648104527855</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Workspaces Migration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c43c1e7a2bb253</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ONTIC TECHNOLOGIES</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7300772b168034de</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intentsify</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
+          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineering Co-op (Cloud)</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>CareConnectMD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea49302adcd1e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform Engineering</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MariaDB plc</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
+          <t>https://www.indeed.com/viewjob?jk=bc29c872e6de963a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - RiskTech</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3011,19 +3011,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
+          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
+          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3081,19 +3081,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3116,29 +3116,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
+          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CareConnectMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,84 +3296,84 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3387,46 +3387,46 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
+          <t>Full-stack Engineer 4, Tech College Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
+          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Arena</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136719f380319c28</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
+          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
+          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
+          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,42 +3646,777 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4 - MLOps</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sony Pictures Entertainment</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Liberty company insurance brokers</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KeHE Distributors</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5 (IC)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5 (IC)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IT Architect – Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Maximus</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Healthcare Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Wider Circle</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KorTerra</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Chanhassen, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Orion Innovation</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>KorTerra</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D110" t="n">
         <v>10.4</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=62838a48fa61a004</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data QA Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4debc3d900a917c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data QA Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-24.xlsx
+++ b/results/job_matches_2026-09-24.xlsx
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/Data Science Eng I</t>
+          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad026bf190602503</t>
+          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
         </is>
       </c>
     </row>
@@ -1308,52 +1308,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cinemark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cinemark</t>
+          <t>FMNE Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FMNE Insurance Company</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Generative AI Technology</t>
+          <t>Associate Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Delta Dental</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer</t>
+          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Delta Dental</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Data Engineer (Oracle Apps)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Oracle Apps)</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
+          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Backend Engineer: Retail Media</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Engineer: Retail Media</t>
+          <t>Azure Databricks Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Architect - DevOps 4D</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd74fc21551185b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
+          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Integration Engineer</t>
+          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SPS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
+          <t>Sr. Data Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>SPS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
+          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
+          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Station Casinos</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c1627cfe23b10</t>
+          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CloudOps</t>
+          <t>Sr. Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Silicon Labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
+          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr. Software Engineer - CloudOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
+          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
+          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Palantir IT Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Palantir IT Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform Engineering</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MariaDB plc</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
+          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
+          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc29c872e6de963a</t>
+          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
+          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
+          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
+          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
         </is>
       </c>
     </row>
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
+          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Full-stack Engineer 4, Tech College Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Tech College Engineering</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
+          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
+          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
+          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
+          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Full Stack Engineer 4 - MLOps</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,15 +3698,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 - MLOps</t>
+          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,24 +3881,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
         </is>
       </c>
     </row>
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>IT Architect – Cloud Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT Architect – Cloud Platform</t>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-24.xlsx
+++ b/results/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (.NET / Java Spring Boot / AWS)</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36f17458475becb</t>
+          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e85b1b7c04ae1c1</t>
+          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/Data Science Eng I</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>WebMobi 360</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3166815bf9267880</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
+          <t>https://www.indeed.com/viewjob?jk=e200e28931966534</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6acf2339423ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
+          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e200e28931966534</t>
+          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Data Engineer I, II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
+          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Giant Eagle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer I, II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
+          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iVedha Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Toronto, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Giant Eagle</t>
+          <t>Cinemark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>FMNE Insurance Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Integration Architect - MS Fabric | Azure Data Factory | Azure Data Bricks | Life Sciences</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
+          <t>https://www.indeed.com/viewjob?jk=62842ac84b93c08c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cinemark</t>
+          <t>Delta Dental</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FMNE Insurance Company</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
+          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Generative AI Technology</t>
+          <t>Data Engineer (Oracle Apps)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
+          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Delta Dental</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
+          <t>Data Engineer Sr (ETL/Alteryx)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
+          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Backend Engineer: Retail Media</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (Oracle Apps)</t>
+          <t>Azure Databricks Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
+          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
+          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Engineer: Retail Media</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
+          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Databricks Administrator</t>
+          <t>Sr. Solution Architect , Data &amp; AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,94 +1791,94 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c99b32ba035506a8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Senior DevOps</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>AltexSoft</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
+          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect - DevOps 4D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464f070dcc86c2c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd74fc21551185b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
+          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Growth Product Engineering</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Architect - DevOps 4D</t>
+          <t>Sr. Data Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>SPS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd74fc21551185b</t>
+          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,242 +2106,242 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
+          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Service Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
+          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
+          <t>Sr. Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Silicon Labs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Integration Engineer</t>
+          <t>Sr. Software Engineer - CloudOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SPS Health</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
+          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
+          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineering Co-op (Cloud)</t>
+          <t>Palantir IT Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea49302adcd1e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Kubernetes Platform Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Silicon Labs</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CloudOps</t>
+          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
+          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
+          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CareConnectMD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcd2d24fae671af</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Palantir IT Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>IT Data Solutions Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81d9ccca3b8cbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform Engineering</t>
+          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MariaDB plc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
+          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Linux Administrator (Ops)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>QuadCode</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa8b81839324a01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
+          <t>Linux Administrator (Ops)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>QuadCode</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a034adc8fdcd3f32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CareConnectMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b908ded2ecce8195</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
+          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
+          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
+          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
+          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
+          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
+          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
+          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4, Tech College Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Tech College Engineering</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
+          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
+          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
         </is>
       </c>
     </row>
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4 - MLOps</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3562,11 +3562,11 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,59 +3646,59 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
+          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 - MLOps</t>
+          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>IT Architect – Cloud Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT Architect – Cloud Platform</t>
+          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Wider Circle</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wider Circle</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4debc3d900a917c2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4205,216 +4205,6 @@
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>KorTerra</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chanhassen, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62838a48fa61a004</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data QA Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4debc3d900a917c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data QA Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
         </is>

--- a/results/job_matches_2026-09-24.xlsx
+++ b/results/job_matches_2026-09-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Databricks</t>
+          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435e38702075f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Platform Admin + Data Engineer</t>
+          <t>AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,112 +741,112 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/Data Science Eng I</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>WebMobi 360</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Vertex AI, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72eb778926f810e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3166815bf9267880</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4abaffce671bae</t>
+          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WebMobi 360</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166815bf9267880</t>
+          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
+          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c7d9bcaaeb50a7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Giant Eagle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
+          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer I, II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
+          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Giant Eagle</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Cinemark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Integration Architect - MS Fabric | Azure Data Factory | Azure Data Bricks | Life Sciences</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
+          <t>https://www.indeed.com/viewjob?jk=62842ac84b93c08c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,129 +1231,129 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f05a1f6b28971e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cinemark</t>
+          <t>Delta Dental</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c30eb9a0b530ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FMNE Insurance Company</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Integration Architect - MS Fabric | Azure Data Factory | Azure Data Bricks | Life Sciences</t>
+          <t>Data Engineer Sr (ETL/Alteryx)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62842ac84b93c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer</t>
+          <t>Backend Engineer: Retail Media</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Delta Dental</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>(Remote) Senior Data &amp; Business Intelligence Engineer</t>
+          <t>Azure Databricks Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Scala, Kafka, Kafka Connect, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286d2cb6ed238709</t>
+          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Cloud Operations Analyst (Oracle)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,182 +1431,182 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=904eb88b47275924</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Oracle Apps)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Care Access</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
+          <t>https://www.indeed.com/viewjob?jk=054dc62f46251118</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Oracle, Cassandra, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad283dad8ab99c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Backend Engineer: Retail Media</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
+          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Databricks Administrator</t>
+          <t>Sr. Solution Architect , Data &amp; AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c99b32ba035506a8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Senior DevOps</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>AltexSoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
+          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect - DevOps 4D</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd74fc21551185b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
+          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eb573e7fc48e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect , Data &amp; AI</t>
+          <t>Data Engineer(Azure) at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99b32ba035506a8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AltexSoft</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Architect - DevOps 4D</t>
+          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,129 +1861,129 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd74fc21551185b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be5cf38ba82ad2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
+          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
+          <t>Senior Data Service Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Integration Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SPS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,112 +1991,112 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4ce506118a2862</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Oats Overnight</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
+          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quantitative Analytics &amp; Model Analyst Senior - Data Operations and Machine Learning Operations</t>
+          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620fde4ff0f5ef0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,42 +2106,42 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Service Developer</t>
+          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
+          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CareConnectMD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
+          <t>IT Data Solutions Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CareConnectMD</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
+          <t>https://www.indeed.com/viewjob?jk=de05f9c575d914fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
+          <t>https://www.indeed.com/viewjob?jk=5e52d983dd64d153</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b908ded2ecce8195</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology (Hybrid- Washington DC)</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1506f9990673e89</t>
+          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Linux Administrator (Ops)</t>
+          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa8b81839324a01</t>
+          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Linux Administrator (Ops)</t>
+          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034adc8fdcd3f32</t>
+          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2801,19 +2801,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b908ded2ecce8195</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c450f2cd054209</t>
+          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Typescript, React, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e84e8c1f5907c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4, DevOps (Network Automation)</t>
+          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f471b3e85c3fae59</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd41c638ce95870</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35849cc2d00cb2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b001d53fe264db52</t>
+          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,84 +3051,84 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3f3d900086713c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2bdd847bee1312</t>
+          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f2ca54167ba8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4 - MLOps</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cb30861c427e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a5fa7db503e14a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2379411eb00f4bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Tech College Engineering</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39c79c83f81aea7</t>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77cdd8808d0a417</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3317,11 +3317,11 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6343db4279b7</t>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99453443ea7ef61f</t>
+          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sony Pictures Entertainment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead32144054a763c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,129 +3436,129 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42a90c3426a05eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Site Reliability Engineer, SecOps</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f22fb50fe2a896e</t>
+          <t>https://www.indeed.com/viewjob?jk=c903ba36fc2337b8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Technical Architect, SMB Pre-Sales</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, API Gateway, RDS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b581e81cd944b048</t>
+          <t>https://www.indeed.com/viewjob?jk=397822b79baee5bd</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5 (Java, Python, Docker, AI) (Enterprise Platforms Technology)</t>
+          <t>Enterprise Software Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>America First Credit Union</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ogden, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Scala, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9322778d99c5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac80251d3b26ae94</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 - MLOps</t>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Wider Circle</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>IT Architect – Cloud Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,462 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>IT Architect – Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Maximus</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>KorTerra</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Chanhassen, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Orion Innovation</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Python/React/Full Stack Engineer (AI &amp; Data Platform)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e76eb12b60f02f24</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Healthcare Data Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Wider Circle</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data QA Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4debc3d900a917c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data QA Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
         </is>
       </c>
     </row>
